--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:39</t>
+    <t xml:space="preserve">2026-09-09 22:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:26</t>
+    <t xml:space="preserve">2026-09-12 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:42</t>
+    <t xml:space="preserve">2026-09-24 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:20</t>
+    <t xml:space="preserve">2026-09-27 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:09</t>
+    <t xml:space="preserve">2026-09-29 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,7 +637,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>38.31</v>
+        <v>383.13</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>38.19</v>
+        <v>381.94</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +671,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34.08</v>
+        <v>340.81</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33.7</v>
+        <v>336.98</v>
       </c>
     </row>
     <row r="6">
@@ -705,7 +705,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.17</v>
+        <v>311.72</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>31.07</v>
+        <v>310.68</v>
       </c>
     </row>
     <row r="8">
@@ -739,7 +739,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>30.55</v>
+        <v>305.49</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>29.45</v>
+        <v>294.48</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +773,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>28.1</v>
+        <v>280.96</v>
       </c>
     </row>
     <row r="11">
@@ -790,7 +790,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>26.98</v>
+        <v>269.77</v>
       </c>
     </row>
     <row r="12">
@@ -807,7 +807,7 @@
         <v>2024</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>26.88</v>
+        <v>268.76</v>
       </c>
     </row>
     <row r="13">
@@ -824,7 +824,7 @@
         <v>2024</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>25.85</v>
+        <v>258.54</v>
       </c>
     </row>
     <row r="14">
@@ -841,7 +841,7 @@
         <v>2024</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>25.47</v>
+        <v>254.65</v>
       </c>
     </row>
     <row r="15">
@@ -858,7 +858,7 @@
         <v>2024</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>25.37</v>
+        <v>253.67</v>
       </c>
     </row>
     <row r="16">
@@ -875,7 +875,7 @@
         <v>2024</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24.4</v>
+        <v>243.97</v>
       </c>
     </row>
     <row r="17">
@@ -892,7 +892,7 @@
         <v>2024</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>23.14</v>
+        <v>231.35</v>
       </c>
     </row>
     <row r="18">
@@ -909,7 +909,7 @@
         <v>2024</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>23.06</v>
+        <v>230.64</v>
       </c>
     </row>
     <row r="19">
@@ -926,7 +926,7 @@
         <v>2024</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>22.91</v>
+        <v>229.12</v>
       </c>
     </row>
     <row r="20">
@@ -943,7 +943,7 @@
         <v>2024</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>22.48</v>
+        <v>224.79</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +960,7 @@
         <v>2024</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>22.35</v>
+        <v>223.47</v>
       </c>
     </row>
     <row r="22">
@@ -977,7 +977,7 @@
         <v>2024</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>22.28</v>
+        <v>222.77</v>
       </c>
     </row>
     <row r="23">
@@ -994,7 +994,7 @@
         <v>2024</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>22.11</v>
+        <v>221.06</v>
       </c>
     </row>
     <row r="24">
@@ -1011,7 +1011,7 @@
         <v>2024</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>22.01</v>
+        <v>220.13</v>
       </c>
     </row>
     <row r="25">
@@ -1028,7 +1028,7 @@
         <v>2024</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>22</v>
+        <v>219.97</v>
       </c>
     </row>
     <row r="26">
@@ -1045,7 +1045,7 @@
         <v>2024</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>21.78</v>
+        <v>217.79</v>
       </c>
     </row>
     <row r="27">
@@ -1062,7 +1062,7 @@
         <v>2024</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>21.45</v>
+        <v>214.48</v>
       </c>
     </row>
     <row r="28">
@@ -1079,7 +1079,7 @@
         <v>2024</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.28</v>
+        <v>212.77</v>
       </c>
     </row>
     <row r="29">
@@ -1096,7 +1096,7 @@
         <v>2024</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21.27</v>
+        <v>212.69</v>
       </c>
     </row>
     <row r="30">
@@ -1113,7 +1113,7 @@
         <v>2024</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>20.72</v>
+        <v>207.15</v>
       </c>
     </row>
     <row r="31">
@@ -1130,7 +1130,7 @@
         <v>2024</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>20.27</v>
+        <v>202.68</v>
       </c>
     </row>
     <row r="32">
@@ -1147,7 +1147,7 @@
         <v>2024</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>20.06</v>
+        <v>200.62</v>
       </c>
     </row>
     <row r="33">
@@ -1164,7 +1164,7 @@
         <v>2024</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>20.04</v>
+        <v>200.38</v>
       </c>
     </row>
     <row r="34">
@@ -1181,7 +1181,7 @@
         <v>2024</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.46</v>
+        <v>194.57</v>
       </c>
     </row>
     <row r="35">
@@ -1198,7 +1198,7 @@
         <v>2024</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>19.31</v>
+        <v>193.11</v>
       </c>
     </row>
     <row r="36">
@@ -1215,7 +1215,7 @@
         <v>2024</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>18.75</v>
+        <v>187.55</v>
       </c>
     </row>
     <row r="37">
@@ -1232,7 +1232,7 @@
         <v>2024</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>18.6</v>
+        <v>185.98</v>
       </c>
     </row>
     <row r="38">
@@ -1249,7 +1249,7 @@
         <v>2024</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>18.52</v>
+        <v>185.2</v>
       </c>
     </row>
     <row r="39">
@@ -1266,7 +1266,7 @@
         <v>2024</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>18.18</v>
+        <v>181.77</v>
       </c>
     </row>
     <row r="40">
@@ -1283,7 +1283,7 @@
         <v>2024</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>18.12</v>
+        <v>181.2</v>
       </c>
     </row>
     <row r="41">
@@ -1300,7 +1300,7 @@
         <v>2024</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>17.64</v>
+        <v>176.43</v>
       </c>
     </row>
     <row r="42">
@@ -1317,7 +1317,7 @@
         <v>2024</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>17.43</v>
+        <v>174.31</v>
       </c>
     </row>
     <row r="43">
@@ -1334,7 +1334,7 @@
         <v>2024</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>17.43</v>
+        <v>174.28</v>
       </c>
     </row>
     <row r="44">
@@ -1351,7 +1351,7 @@
         <v>2024</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>17.36</v>
+        <v>173.61</v>
       </c>
     </row>
     <row r="45">
@@ -1368,7 +1368,7 @@
         <v>2024</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>17.35</v>
+        <v>173.48</v>
       </c>
     </row>
     <row r="46">
@@ -1385,7 +1385,7 @@
         <v>2024</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>17.23</v>
+        <v>172.31</v>
       </c>
     </row>
     <row r="47">
@@ -1402,7 +1402,7 @@
         <v>2024</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>17.05</v>
+        <v>170.55</v>
       </c>
     </row>
     <row r="48">
@@ -1419,7 +1419,7 @@
         <v>2024</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>17.03</v>
+        <v>170.27</v>
       </c>
     </row>
     <row r="49">
@@ -1436,7 +1436,7 @@
         <v>2024</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>16.75</v>
+        <v>167.52</v>
       </c>
     </row>
     <row r="50">
@@ -1453,7 +1453,7 @@
         <v>2024</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>16.52</v>
+        <v>165.18</v>
       </c>
     </row>
     <row r="51">
@@ -1470,7 +1470,7 @@
         <v>2024</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>15.35</v>
+        <v>153.54</v>
       </c>
     </row>
     <row r="52">
@@ -1487,7 +1487,7 @@
         <v>2024</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>15.09</v>
+        <v>150.93</v>
       </c>
     </row>
     <row r="53">
@@ -1504,7 +1504,7 @@
         <v>2024</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>11.17</v>
+        <v>111.69</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:04</t>
+    <t xml:space="preserve">2026-10-01 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:28</t>
+    <t xml:space="preserve">2026-10-02 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:10</t>
+    <t xml:space="preserve">2026-10-05 07:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
